--- a/data/ydavila.xlsx
+++ b/data/ydavila.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/Resumen/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{9D0DB320-8165-4D9C-9CD7-014CA6C6BE04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B77316D-3372-43FA-B188-4923EC6BD4D7}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{9D0DB320-8165-4D9C-9CD7-014CA6C6BE04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA445E85-9779-4277-BE5C-1D798174BC35}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{08AA2194-8E1D-4AF5-8E4B-B1A25E802466}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="17">
   <si>
     <t>Fecha</t>
   </si>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C14C1A3-FF3F-44C6-A5D8-852807A834FA}">
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -2789,35 +2789,219 @@
         <v>15</v>
       </c>
       <c r="D51" s="4">
-        <f t="shared" ref="D51" si="90">+D50+K50+E50-F50</f>
+        <f t="shared" ref="D51:D55" si="90">+D50+K50+E50-F50</f>
         <v>13804.537999999997</v>
+      </c>
+      <c r="G51" s="2">
+        <v>193.26</v>
       </c>
       <c r="H51" s="5">
         <f t="shared" si="83"/>
-        <v>9782.82</v>
+        <v>9976.08</v>
       </c>
       <c r="I51" s="5">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>19.326000000000001</v>
       </c>
       <c r="J51" s="5">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>19.326000000000001</v>
       </c>
       <c r="K51" s="5">
         <f t="shared" si="86"/>
-        <v>0</v>
+        <v>173.934</v>
       </c>
       <c r="L51" s="5">
         <f t="shared" si="87"/>
-        <v>8804.5379999999986</v>
+        <v>8978.4719999999979</v>
       </c>
       <c r="M51" s="5">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>5.7977999999999996</v>
       </c>
       <c r="N51" s="6">
         <f t="shared" si="89"/>
+        <v>1.3999744142107475E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <v>45902</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="4">
+        <f t="shared" si="90"/>
+        <v>13978.471999999996</v>
+      </c>
+      <c r="G52" s="2">
+        <v>321.5</v>
+      </c>
+      <c r="H52" s="5">
+        <f t="shared" ref="H52:H55" si="91">+H51+G52</f>
+        <v>10297.58</v>
+      </c>
+      <c r="I52" s="5">
+        <f t="shared" ref="I52:I55" si="92">+G52*0.1</f>
+        <v>32.15</v>
+      </c>
+      <c r="J52" s="5">
+        <f t="shared" ref="J52:J55" si="93">+I52</f>
+        <v>32.15</v>
+      </c>
+      <c r="K52" s="5">
+        <f t="shared" ref="K52:K55" si="94">+G52-I52</f>
+        <v>289.35000000000002</v>
+      </c>
+      <c r="L52" s="5">
+        <f t="shared" ref="L52:L55" si="95">+L51+K52</f>
+        <v>9267.8219999999983</v>
+      </c>
+      <c r="M52" s="5">
+        <f t="shared" ref="M52:M55" si="96">+K52/30</f>
+        <v>9.6450000000000014</v>
+      </c>
+      <c r="N52" s="6">
+        <f t="shared" ref="N52:N55" si="97">+G52/D52</f>
+        <v>2.2999652608668535E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <v>45932</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="4">
+        <f t="shared" si="90"/>
+        <v>14267.821999999996</v>
+      </c>
+      <c r="G53" s="2">
+        <v>299.62</v>
+      </c>
+      <c r="H53" s="5">
+        <f t="shared" si="91"/>
+        <v>10597.2</v>
+      </c>
+      <c r="I53" s="5">
+        <f t="shared" si="92"/>
+        <v>29.962000000000003</v>
+      </c>
+      <c r="J53" s="5">
+        <f t="shared" si="93"/>
+        <v>29.962000000000003</v>
+      </c>
+      <c r="K53" s="5">
+        <f t="shared" si="94"/>
+        <v>269.65800000000002</v>
+      </c>
+      <c r="L53" s="5">
+        <f t="shared" si="95"/>
+        <v>9537.4799999999977</v>
+      </c>
+      <c r="M53" s="5">
+        <f t="shared" si="96"/>
+        <v>8.9885999999999999</v>
+      </c>
+      <c r="N53" s="6">
+        <f t="shared" si="97"/>
+        <v>2.0999701285872509E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <v>45963</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="4">
+        <f t="shared" si="90"/>
+        <v>14537.479999999996</v>
+      </c>
+      <c r="G54" s="2">
+        <v>523.35</v>
+      </c>
+      <c r="H54" s="5">
+        <f t="shared" si="91"/>
+        <v>11120.550000000001</v>
+      </c>
+      <c r="I54" s="5">
+        <f t="shared" si="92"/>
+        <v>52.335000000000008</v>
+      </c>
+      <c r="J54" s="5">
+        <f t="shared" si="93"/>
+        <v>52.335000000000008</v>
+      </c>
+      <c r="K54" s="5">
+        <f t="shared" si="94"/>
+        <v>471.01499999999999</v>
+      </c>
+      <c r="L54" s="5">
+        <f t="shared" si="95"/>
+        <v>10008.494999999997</v>
+      </c>
+      <c r="M54" s="5">
+        <f t="shared" si="96"/>
+        <v>15.7005</v>
+      </c>
+      <c r="N54" s="6">
+        <f t="shared" si="97"/>
+        <v>3.6000049527153272E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <v>45993</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="4">
+        <f t="shared" si="90"/>
+        <v>15008.494999999995</v>
+      </c>
+      <c r="H55" s="5">
+        <f t="shared" si="91"/>
+        <v>11120.550000000001</v>
+      </c>
+      <c r="I55" s="5">
+        <f t="shared" si="92"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="5">
+        <f t="shared" si="93"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="5">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="L55" s="5">
+        <f t="shared" si="95"/>
+        <v>10008.494999999997</v>
+      </c>
+      <c r="M55" s="5">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="N55" s="6">
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
     </row>

--- a/data/ydavila.xlsx
+++ b/data/ydavila.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Documentos\Proyectos\FIFI\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/Proyectos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADCEA75E-BC5C-4A97-B647-33E437DD99E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{ADCEA75E-BC5C-4A97-B647-33E437DD99E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F5E40D9-A5FE-4605-A4B4-D7069659E3C7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{08AA2194-8E1D-4AF5-8E4B-B1A25E802466}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="17">
   <si>
     <t>Fecha</t>
   </si>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C14C1A3-FF3F-44C6-A5D8-852807A834FA}">
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -3114,33 +3114,174 @@
         <f t="shared" si="98"/>
         <v>15767.059999999994</v>
       </c>
+      <c r="G58" s="2">
+        <v>204</v>
+      </c>
       <c r="H58" s="5">
         <f t="shared" si="99"/>
-        <v>11963.400000000001</v>
+        <v>12167.400000000001</v>
       </c>
       <c r="I58" s="5">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>20.400000000000002</v>
       </c>
       <c r="J58" s="5">
         <f t="shared" si="101"/>
-        <v>0</v>
+        <v>20.400000000000002</v>
       </c>
       <c r="K58" s="5">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>183.6</v>
       </c>
       <c r="L58" s="5">
         <f t="shared" si="103"/>
-        <v>10767.059999999996</v>
+        <v>10950.659999999996</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="N58" s="6">
         <f t="shared" si="105"/>
-        <v>0</v>
+        <v>1.2938366442443935E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <v>46114</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="4">
+        <f t="shared" ref="D59:D61" si="106">+D58+K58+E58-F58</f>
+        <v>15950.659999999994</v>
+      </c>
+      <c r="G59" s="2">
+        <v>106.89</v>
+      </c>
+      <c r="H59" s="5">
+        <f t="shared" ref="H59:H61" si="107">+H58+G59</f>
+        <v>12274.29</v>
+      </c>
+      <c r="I59" s="5">
+        <f t="shared" ref="I59:I61" si="108">+G59*0.1</f>
+        <v>10.689</v>
+      </c>
+      <c r="J59" s="5">
+        <f t="shared" ref="J59:J61" si="109">+I59</f>
+        <v>10.689</v>
+      </c>
+      <c r="K59" s="5">
+        <f t="shared" ref="K59:K61" si="110">+G59-I59</f>
+        <v>96.200999999999993</v>
+      </c>
+      <c r="L59" s="5">
+        <f t="shared" ref="L59:L61" si="111">+L58+K59</f>
+        <v>11046.860999999995</v>
+      </c>
+      <c r="M59" s="5">
+        <f t="shared" ref="M59:M61" si="112">+K59/30</f>
+        <v>3.2066999999999997</v>
+      </c>
+      <c r="N59" s="6">
+        <f t="shared" ref="N59:N61" si="113">+G59/D59</f>
+        <v>6.7012901033562267E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="3">
+        <v>46144</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="4">
+        <f t="shared" si="106"/>
+        <v>16046.860999999994</v>
+      </c>
+      <c r="G60" s="2">
+        <v>379.99</v>
+      </c>
+      <c r="H60" s="5">
+        <f t="shared" si="107"/>
+        <v>12654.28</v>
+      </c>
+      <c r="I60" s="5">
+        <f t="shared" si="108"/>
+        <v>37.999000000000002</v>
+      </c>
+      <c r="J60" s="5">
+        <f t="shared" si="109"/>
+        <v>37.999000000000002</v>
+      </c>
+      <c r="K60" s="5">
+        <f t="shared" si="110"/>
+        <v>341.99099999999999</v>
+      </c>
+      <c r="L60" s="5">
+        <f t="shared" si="111"/>
+        <v>11388.851999999995</v>
+      </c>
+      <c r="M60" s="5">
+        <f t="shared" si="112"/>
+        <v>11.399699999999999</v>
+      </c>
+      <c r="N60" s="6">
+        <f t="shared" si="113"/>
+        <v>2.3680020659492231E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" s="4">
+        <f t="shared" si="106"/>
+        <v>16388.851999999992</v>
+      </c>
+      <c r="G61" s="2">
+        <v>297.17</v>
+      </c>
+      <c r="H61" s="5">
+        <f t="shared" si="107"/>
+        <v>12951.45</v>
+      </c>
+      <c r="I61" s="5">
+        <f t="shared" si="108"/>
+        <v>29.717000000000002</v>
+      </c>
+      <c r="J61" s="5">
+        <f t="shared" si="109"/>
+        <v>29.717000000000002</v>
+      </c>
+      <c r="K61" s="5">
+        <f t="shared" si="110"/>
+        <v>267.45300000000003</v>
+      </c>
+      <c r="L61" s="5">
+        <f t="shared" si="111"/>
+        <v>11656.304999999995</v>
+      </c>
+      <c r="M61" s="5">
+        <f t="shared" si="112"/>
+        <v>8.9151000000000007</v>
+      </c>
+      <c r="N61" s="6">
+        <f t="shared" si="113"/>
+        <v>1.8132447593034593E-2</v>
       </c>
     </row>
   </sheetData>
